--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382947</v>
+        <v>122382509</v>
       </c>
       <c r="B3" t="n">
         <v>78645</v>
@@ -846,21 +846,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482090</v>
+        <v>482086</v>
       </c>
       <c r="R3" t="n">
-        <v>6989515</v>
+        <v>6989656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,11 +890,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -949,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382509</v>
+        <v>122382855</v>
       </c>
       <c r="B4" t="n">
         <v>78645</v>
@@ -989,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482086</v>
+        <v>482156</v>
       </c>
       <c r="R4" t="n">
-        <v>6989656</v>
+        <v>6989544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1051,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382855</v>
+        <v>122382806</v>
       </c>
       <c r="B5" t="n">
         <v>78645</v>
@@ -1091,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482156</v>
+        <v>482185</v>
       </c>
       <c r="R5" t="n">
-        <v>6989544</v>
+        <v>6989555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382806</v>
+        <v>122382555</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482185</v>
+        <v>482112</v>
       </c>
       <c r="R6" t="n">
-        <v>6989555</v>
+        <v>6989732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,6 +1201,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,6 +1214,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382555</v>
+        <v>122382695</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482112</v>
+        <v>482171</v>
       </c>
       <c r="R7" t="n">
-        <v>6989732</v>
+        <v>6989724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,11 +1333,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,31 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382695</v>
+        <v>122382450</v>
       </c>
       <c r="B8" t="n">
         <v>78645</v>
@@ -1432,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482171</v>
+        <v>482079</v>
       </c>
       <c r="R8" t="n">
-        <v>6989724</v>
+        <v>6989620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382450</v>
+        <v>122382014</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482079</v>
+        <v>482005</v>
       </c>
       <c r="R9" t="n">
-        <v>6989620</v>
+        <v>6989579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,6 +1542,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1580,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382014</v>
+        <v>122382947</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,27 +1612,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482005</v>
+        <v>482090</v>
       </c>
       <c r="R10" t="n">
-        <v>6989579</v>
+        <v>6989515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1730,6 +1730,141 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122397733</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90797</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Håkansgårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>482158</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6989694</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382765</v>
+        <v>122382450</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482158</v>
+        <v>482079</v>
       </c>
       <c r="R2" t="n">
-        <v>6989694</v>
+        <v>6989620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår vid stambasen.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382509</v>
+        <v>122382695</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -852,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482086</v>
+        <v>482171</v>
       </c>
       <c r="R3" t="n">
-        <v>6989656</v>
+        <v>6989724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382855</v>
+        <v>122382014</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482156</v>
+        <v>482005</v>
       </c>
       <c r="R4" t="n">
-        <v>6989544</v>
+        <v>6989579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +962,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,6 +975,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382806</v>
+        <v>122382509</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482185</v>
+        <v>482086</v>
       </c>
       <c r="R5" t="n">
-        <v>6989555</v>
+        <v>6989656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382695</v>
+        <v>122382765</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482171</v>
+        <v>482158</v>
       </c>
       <c r="R7" t="n">
-        <v>6989724</v>
+        <v>6989694</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,6 +1338,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1341,6 +1351,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382450</v>
+        <v>122382855</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482079</v>
+        <v>482156</v>
       </c>
       <c r="R8" t="n">
-        <v>6989620</v>
+        <v>6989544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382014</v>
+        <v>122382806</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482005</v>
+        <v>482185</v>
       </c>
       <c r="R9" t="n">
-        <v>6989579</v>
+        <v>6989555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,11 +1572,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,31 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1599,7 +1599,7 @@
         <v>122382947</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>122397733</v>
       </c>
       <c r="B11" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382450</v>
+        <v>122382509</v>
       </c>
       <c r="B2" t="n">
         <v>78646</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482079</v>
+        <v>482086</v>
       </c>
       <c r="R2" t="n">
-        <v>6989620</v>
+        <v>6989656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382695</v>
+        <v>122382450</v>
       </c>
       <c r="B3" t="n">
         <v>78646</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482171</v>
+        <v>482079</v>
       </c>
       <c r="R3" t="n">
-        <v>6989724</v>
+        <v>6989620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382509</v>
+        <v>122382555</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482086</v>
+        <v>482112</v>
       </c>
       <c r="R5" t="n">
-        <v>6989656</v>
+        <v>6989732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1099,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1102,6 +1112,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382555</v>
+        <v>122382855</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482112</v>
+        <v>482156</v>
       </c>
       <c r="R6" t="n">
-        <v>6989732</v>
+        <v>6989544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,11 +1231,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1214,31 +1239,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382765</v>
+        <v>122382806</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482158</v>
+        <v>482185</v>
       </c>
       <c r="R7" t="n">
-        <v>6989694</v>
+        <v>6989555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,11 +1333,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår vid stambasen.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,31 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382855</v>
+        <v>122382695</v>
       </c>
       <c r="B8" t="n">
         <v>78646</v>
@@ -1432,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482156</v>
+        <v>482171</v>
       </c>
       <c r="R8" t="n">
-        <v>6989544</v>
+        <v>6989724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382806</v>
+        <v>122382765</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482185</v>
+        <v>482158</v>
       </c>
       <c r="R9" t="n">
-        <v>6989555</v>
+        <v>6989694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,6 +1542,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1580,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1612,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R10" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,6 +1692,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1708,14 +1711,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B11" t="n">
-        <v>90807</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,41 +1747,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R11" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,7 +1825,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1848,9 +1843,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122382509</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382450</v>
+        <v>122382765</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482079</v>
+        <v>482158</v>
       </c>
       <c r="R3" t="n">
-        <v>6989620</v>
+        <v>6989694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +860,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +873,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382014</v>
+        <v>122382450</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482005</v>
+        <v>482079</v>
       </c>
       <c r="R4" t="n">
-        <v>6989579</v>
+        <v>6989620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,11 +992,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,31 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,7 +1019,7 @@
         <v>122382555</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>122382855</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>122382806</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>122382695</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382765</v>
+        <v>122382014</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482158</v>
+        <v>482005</v>
       </c>
       <c r="R9" t="n">
-        <v>6989694</v>
+        <v>6989579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackspår vid stambasen.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
         <v>122397733</v>
       </c>
       <c r="B10" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>122382947</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382765</v>
+        <v>122382014</v>
       </c>
       <c r="B3" t="n">
         <v>57395</v>
@@ -813,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482158</v>
+        <v>482005</v>
       </c>
       <c r="R3" t="n">
-        <v>6989694</v>
+        <v>6989579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår vid stambasen.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +891,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382555</v>
+        <v>122382765</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482112</v>
+        <v>482158</v>
       </c>
       <c r="R5" t="n">
-        <v>6989732</v>
+        <v>6989694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackspår och avskalad bark.</t>
+          <t>Hackspår vid stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382806</v>
+        <v>122382555</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482185</v>
+        <v>482112</v>
       </c>
       <c r="R7" t="n">
-        <v>6989555</v>
+        <v>6989732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,6 +1338,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1341,6 +1351,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1459,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382014</v>
+        <v>122382806</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482005</v>
+        <v>482185</v>
       </c>
       <c r="R9" t="n">
-        <v>6989579</v>
+        <v>6989555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,11 +1572,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,31 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B10" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,41 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R10" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1681,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1690,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1711,9 +1708,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1731,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,39 +1749,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R11" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1820,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,6 +1829,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1843,14 +1848,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122382509</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382014</v>
+        <v>122382555</v>
       </c>
       <c r="B3" t="n">
         <v>57395</v>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>100049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -813,7 +803,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482005</v>
+        <v>482112</v>
       </c>
       <c r="R3" t="n">
-        <v>6989579</v>
+        <v>6989732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Hackspår och avskalad bark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,11 +869,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -891,12 +876,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382450</v>
+        <v>122382695</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,11 +917,6 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -954,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482079</v>
+        <v>482171</v>
       </c>
       <c r="R4" t="n">
-        <v>6989620</v>
+        <v>6989724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,11 +1014,6 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1116,11 +1091,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1153,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382855</v>
+        <v>122382450</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,11 +1141,6 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1193,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482156</v>
+        <v>482079</v>
       </c>
       <c r="R6" t="n">
-        <v>6989544</v>
+        <v>6989620</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382555</v>
+        <v>122382806</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1236,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482112</v>
+        <v>482185</v>
       </c>
       <c r="R7" t="n">
-        <v>6989732</v>
+        <v>6989555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,11 +1293,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,31 +1301,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382695</v>
+        <v>122382014</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,34 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482171</v>
+        <v>482005</v>
       </c>
       <c r="R8" t="n">
-        <v>6989724</v>
+        <v>6989579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,6 +1395,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1478,6 +1408,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382806</v>
+        <v>122382855</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,11 +1462,6 @@
       <c r="E9" t="n">
         <v>6425</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1534,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482185</v>
+        <v>482156</v>
       </c>
       <c r="R9" t="n">
-        <v>6989555</v>
+        <v>6989544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1557,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R10" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,6 +1632,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1698,24 +1641,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B11" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,41 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R11" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1746,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,7 +1755,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1838,19 +1763,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382509</v>
+        <v>122382450</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482086</v>
+        <v>482079</v>
       </c>
       <c r="R2" t="n">
-        <v>6989656</v>
+        <v>6989620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382555</v>
+        <v>122382855</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482112</v>
+        <v>482156</v>
       </c>
       <c r="R3" t="n">
-        <v>6989732</v>
+        <v>6989544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +855,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,26 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382695</v>
+        <v>122382509</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,6 +897,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482171</v>
+        <v>482086</v>
       </c>
       <c r="R4" t="n">
-        <v>6989724</v>
+        <v>6989656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382765</v>
+        <v>122382555</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,6 +999,11 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482158</v>
+        <v>482112</v>
       </c>
       <c r="R5" t="n">
-        <v>6989694</v>
+        <v>6989732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackspår vid stambasen.</t>
+          <t>Hackspår och avskalad bark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,6 +1081,11 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382450</v>
+        <v>122382765</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,29 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482079</v>
+        <v>482158</v>
       </c>
       <c r="R6" t="n">
-        <v>6989620</v>
+        <v>6989694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1201,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1204,6 +1214,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382806</v>
+        <v>122382695</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,6 +1273,11 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1255,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482185</v>
+        <v>482171</v>
       </c>
       <c r="R7" t="n">
-        <v>6989555</v>
+        <v>6989724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382014</v>
+        <v>122382806</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,34 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482005</v>
+        <v>482185</v>
       </c>
       <c r="R8" t="n">
-        <v>6989579</v>
+        <v>6989555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,11 +1435,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1408,26 +1443,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1444,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382855</v>
+        <v>122382014</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,29 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482156</v>
+        <v>482005</v>
       </c>
       <c r="R9" t="n">
-        <v>6989544</v>
+        <v>6989579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,6 +1542,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1525,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1541,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B10" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,36 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R10" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1681,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1690,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,14 +1698,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1666,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,34 +1749,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R11" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1820,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,6 +1829,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1763,19 +1838,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382450</v>
+        <v>122382806</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482079</v>
+        <v>482185</v>
       </c>
       <c r="R2" t="n">
-        <v>6989620</v>
+        <v>6989555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382855</v>
+        <v>122382509</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482156</v>
+        <v>482086</v>
       </c>
       <c r="R3" t="n">
-        <v>6989544</v>
+        <v>6989656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382509</v>
+        <v>122382450</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482086</v>
+        <v>482079</v>
       </c>
       <c r="R4" t="n">
-        <v>6989656</v>
+        <v>6989620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382555</v>
+        <v>122382855</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482112</v>
+        <v>482156</v>
       </c>
       <c r="R5" t="n">
-        <v>6989732</v>
+        <v>6989544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,11 +1059,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,31 +1067,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1255,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382695</v>
+        <v>122382014</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482171</v>
+        <v>482005</v>
       </c>
       <c r="R7" t="n">
-        <v>6989724</v>
+        <v>6989579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,6 +1303,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1341,6 +1316,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382806</v>
+        <v>122382555</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482185</v>
+        <v>482112</v>
       </c>
       <c r="R8" t="n">
-        <v>6989555</v>
+        <v>6989732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,6 +1440,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1443,6 +1453,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1459,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382014</v>
+        <v>122382695</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482005</v>
+        <v>482171</v>
       </c>
       <c r="R9" t="n">
-        <v>6989579</v>
+        <v>6989724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,11 +1572,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,31 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1612,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R10" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,6 +1692,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1708,14 +1711,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B11" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,41 +1747,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R11" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,7 +1825,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1848,9 +1843,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382509</v>
+        <v>122382855</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482086</v>
+        <v>482156</v>
       </c>
       <c r="R3" t="n">
-        <v>6989656</v>
+        <v>6989544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382450</v>
+        <v>122382555</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482079</v>
+        <v>482112</v>
       </c>
       <c r="R4" t="n">
-        <v>6989620</v>
+        <v>6989732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,6 +962,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +975,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382855</v>
+        <v>122382765</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482156</v>
+        <v>482158</v>
       </c>
       <c r="R5" t="n">
-        <v>6989544</v>
+        <v>6989694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,6 +1099,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1067,6 +1112,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382765</v>
+        <v>122382509</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482158</v>
+        <v>482086</v>
       </c>
       <c r="R6" t="n">
-        <v>6989694</v>
+        <v>6989656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,11 +1231,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackspår vid stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1179,31 +1239,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382014</v>
+        <v>122382450</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482005</v>
+        <v>482079</v>
       </c>
       <c r="R7" t="n">
-        <v>6989579</v>
+        <v>6989620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,11 +1333,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1316,31 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382555</v>
+        <v>122382014</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1393,7 +1393,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482112</v>
+        <v>482005</v>
       </c>
       <c r="R8" t="n">
-        <v>6989732</v>
+        <v>6989579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hackspår och avskalad bark.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382450</v>
+        <v>122382014</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482079</v>
+        <v>482005</v>
       </c>
       <c r="R7" t="n">
-        <v>6989620</v>
+        <v>6989579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,6 +1338,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1341,6 +1351,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382014</v>
+        <v>122382450</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482005</v>
+        <v>482079</v>
       </c>
       <c r="R8" t="n">
-        <v>6989579</v>
+        <v>6989620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,11 +1470,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1453,31 +1478,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382806</v>
+        <v>122382555</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482185</v>
+        <v>482112</v>
       </c>
       <c r="R2" t="n">
-        <v>6989555</v>
+        <v>6989732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382855</v>
+        <v>122382014</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +828,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482156</v>
+        <v>482005</v>
       </c>
       <c r="R3" t="n">
-        <v>6989544</v>
+        <v>6989579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +895,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +908,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382555</v>
+        <v>122382806</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +965,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482112</v>
+        <v>482185</v>
       </c>
       <c r="R4" t="n">
-        <v>6989732</v>
+        <v>6989555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,11 +1027,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,31 +1035,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382765</v>
+        <v>122382450</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482158</v>
+        <v>482079</v>
       </c>
       <c r="R5" t="n">
-        <v>6989694</v>
+        <v>6989620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,11 +1129,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår vid stambasen.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1112,31 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382509</v>
+        <v>122382695</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482086</v>
+        <v>482171</v>
       </c>
       <c r="R6" t="n">
-        <v>6989656</v>
+        <v>6989724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382014</v>
+        <v>122382765</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1291,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482005</v>
+        <v>482158</v>
       </c>
       <c r="R7" t="n">
-        <v>6989579</v>
+        <v>6989694</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Hackspår vid stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382450</v>
+        <v>122382509</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482079</v>
+        <v>482086</v>
       </c>
       <c r="R8" t="n">
-        <v>6989620</v>
+        <v>6989656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382695</v>
+        <v>122382855</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482171</v>
+        <v>482156</v>
       </c>
       <c r="R9" t="n">
-        <v>6989724</v>
+        <v>6989544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B10" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,41 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R10" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1681,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1690,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1711,9 +1708,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1731,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,39 +1749,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R11" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1820,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,6 +1829,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1843,14 +1848,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382555</v>
+        <v>122382806</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482112</v>
+        <v>482185</v>
       </c>
       <c r="R2" t="n">
-        <v>6989732</v>
+        <v>6989555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382014</v>
+        <v>122382855</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482005</v>
+        <v>482156</v>
       </c>
       <c r="R3" t="n">
-        <v>6989579</v>
+        <v>6989544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,11 +855,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,31 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -949,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382806</v>
+        <v>122382509</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -989,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482185</v>
+        <v>482086</v>
       </c>
       <c r="R4" t="n">
-        <v>6989555</v>
+        <v>6989656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1255,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382765</v>
+        <v>122382014</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1291,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482158</v>
+        <v>482005</v>
       </c>
       <c r="R7" t="n">
-        <v>6989694</v>
+        <v>6989579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1270,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår vid stambasen.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,12 +1299,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382509</v>
+        <v>122382765</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,34 +1338,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482086</v>
+        <v>482158</v>
       </c>
       <c r="R8" t="n">
-        <v>6989656</v>
+        <v>6989694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,6 +1405,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1478,6 +1418,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382855</v>
+        <v>122382555</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482156</v>
+        <v>482112</v>
       </c>
       <c r="R9" t="n">
-        <v>6989544</v>
+        <v>6989732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,6 +1542,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår och avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1580,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382806</v>
+        <v>122382855</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482185</v>
+        <v>482156</v>
       </c>
       <c r="R2" t="n">
-        <v>6989555</v>
+        <v>6989544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382855</v>
+        <v>122382014</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482156</v>
+        <v>482005</v>
       </c>
       <c r="R3" t="n">
-        <v>6989544</v>
+        <v>6989579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +860,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +873,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122382509</v>
+        <v>122382450</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482086</v>
+        <v>482079</v>
       </c>
       <c r="R4" t="n">
-        <v>6989656</v>
+        <v>6989620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382450</v>
+        <v>122382509</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482079</v>
+        <v>482086</v>
       </c>
       <c r="R5" t="n">
-        <v>6989620</v>
+        <v>6989656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1121,7 @@
         <v>122382695</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382014</v>
+        <v>122382555</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,7 +1256,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482005</v>
+        <v>482112</v>
       </c>
       <c r="R7" t="n">
-        <v>6989579</v>
+        <v>6989732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Hackspår och avskalad bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,12 +1334,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1325,7 +1360,7 @@
         <v>122382765</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1459,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382555</v>
+        <v>122382806</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482112</v>
+        <v>482185</v>
       </c>
       <c r="R9" t="n">
-        <v>6989732</v>
+        <v>6989555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,11 +1572,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,31 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1599,7 +1599,7 @@
         <v>122382947</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>122397733</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382855</v>
+        <v>122382695</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482156</v>
+        <v>482171</v>
       </c>
       <c r="R2" t="n">
-        <v>6989544</v>
+        <v>6989724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382014</v>
+        <v>122382555</v>
       </c>
       <c r="B3" t="n">
         <v>57400</v>
@@ -813,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482005</v>
+        <v>482112</v>
       </c>
       <c r="R3" t="n">
-        <v>6989579</v>
+        <v>6989732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Hackspår och avskalad bark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +891,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>122382450</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382509</v>
+        <v>122382014</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482086</v>
+        <v>482005</v>
       </c>
       <c r="R5" t="n">
-        <v>6989656</v>
+        <v>6989579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1099,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1102,6 +1112,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382695</v>
+        <v>122382806</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482171</v>
+        <v>482185</v>
       </c>
       <c r="R6" t="n">
-        <v>6989724</v>
+        <v>6989555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382555</v>
+        <v>122382855</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482112</v>
+        <v>482156</v>
       </c>
       <c r="R7" t="n">
-        <v>6989732</v>
+        <v>6989544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,11 +1333,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår och avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1316,31 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122382765</v>
+        <v>122382509</v>
       </c>
       <c r="B8" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482158</v>
+        <v>482086</v>
       </c>
       <c r="R8" t="n">
-        <v>6989694</v>
+        <v>6989656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,11 +1435,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår vid stambasen.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1453,31 +1443,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382806</v>
+        <v>122382765</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482185</v>
+        <v>482158</v>
       </c>
       <c r="R9" t="n">
-        <v>6989555</v>
+        <v>6989694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,6 +1542,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår vid stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1580,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122382947</v>
+        <v>122397733</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1612,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482090</v>
+        <v>482158</v>
       </c>
       <c r="R10" t="n">
-        <v>6989515</v>
+        <v>6989694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,6 +1692,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1708,14 +1711,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397733</v>
+        <v>122382947</v>
       </c>
       <c r="B11" t="n">
-        <v>90852</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,41 +1747,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482158</v>
+        <v>482090</v>
       </c>
       <c r="R11" t="n">
-        <v>6989694</v>
+        <v>6989515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,7 +1825,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1848,9 +1843,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 31448-2024 artfynd.xlsx
+++ b/artfynd/A 31448-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122382695</v>
+        <v>122382806</v>
       </c>
       <c r="B2" t="n">
         <v>78660</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482171</v>
+        <v>482185</v>
       </c>
       <c r="R2" t="n">
-        <v>6989724</v>
+        <v>6989555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122382555</v>
+        <v>122382765</v>
       </c>
       <c r="B3" t="n">
         <v>57400</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482112</v>
+        <v>482158</v>
       </c>
       <c r="R3" t="n">
-        <v>6989732</v>
+        <v>6989694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår och avskalad bark.</t>
+          <t>Hackspår vid stambasen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122382014</v>
+        <v>122382555</v>
       </c>
       <c r="B5" t="n">
         <v>57400</v>
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482005</v>
+        <v>482112</v>
       </c>
       <c r="R5" t="n">
-        <v>6989579</v>
+        <v>6989732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Hackspår och avskalad bark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122382806</v>
+        <v>122382014</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,34 +1169,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482185</v>
+        <v>482005</v>
       </c>
       <c r="R6" t="n">
-        <v>6989555</v>
+        <v>6989579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,6 +1236,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,6 +1249,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122382855</v>
+        <v>122382695</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1295,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482156</v>
+        <v>482171</v>
       </c>
       <c r="R7" t="n">
-        <v>6989544</v>
+        <v>6989724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1459,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122382765</v>
+        <v>122382855</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482158</v>
+        <v>482156</v>
       </c>
       <c r="R9" t="n">
-        <v>6989694</v>
+        <v>6989544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,11 +1572,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår vid stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,31 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
